--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32A7769F-FB5F-4EF5-B2A4-F4D7394B7B31}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,6 +199,27 @@
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subhrim </t>
+  </si>
+  <si>
+    <t>aug</t>
+  </si>
+  <si>
+    <t>d2537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bad  </t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extremely tired </t>
   </si>
 </sst>
 </file>
@@ -885,26 +906,34 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>54</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12517276</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -1016,26 +1045,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B7" s="14">
+        <v>420</v>
+      </c>
+      <c r="C7" s="14">
+        <v>45</v>
+      </c>
+      <c r="D7" s="14">
+        <v>120</v>
+      </c>
+      <c r="E7" s="14">
+        <v>200</v>
+      </c>
+      <c r="F7" s="14">
+        <v>300</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14">
+        <v>300</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1385</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>55</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>

--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32A7769F-FB5F-4EF5-B2A4-F4D7394B7B31}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23DC8CDE-53D8-4D98-BA28-781673B82F5C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t xml:space="preserve">extremely tired </t>
+  </si>
+  <si>
+    <t xml:space="preserve">satisfied </t>
   </si>
 </sst>
 </file>
@@ -1091,24 +1094,44 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>45</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>100</v>
+      </c>
+      <c r="F8" s="14">
+        <v>200</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>400</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1285</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
+        <v>155</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="M8" s="16"/>
       <c r="N8" s="17"/>
     </row>

--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23DC8CDE-53D8-4D98-BA28-781673B82F5C}"/>
+  <xr:revisionPtr revIDLastSave="298" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF1C6184-BFA1-4462-AA6E-BD26033A067E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t xml:space="preserve">satisfied </t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>bad</t>
   </si>
 </sst>
 </file>
@@ -503,6 +509,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1049,7 +1059,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="13">
-        <v>46254</v>
+        <v>46235</v>
       </c>
       <c r="B7" s="14">
         <v>420</v>
@@ -1064,21 +1074,21 @@
         <v>200</v>
       </c>
       <c r="F7" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G7" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14">
         <v>300</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>1385</v>
+        <v>1085</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>355</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>57</v>
@@ -1095,7 +1105,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
-        <v>46255</v>
+        <v>46236</v>
       </c>
       <c r="B8" s="14">
         <v>420</v>
@@ -1110,21 +1120,21 @@
         <v>100</v>
       </c>
       <c r="F8" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G8" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" s="14">
         <v>400</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>1285</v>
+        <v>1085</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>155</v>
+        <v>355</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>49</v>
@@ -1132,69 +1142,137 @@
       <c r="L8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+      <c r="M8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46237</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>45</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>200</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14">
+        <v>4</v>
+      </c>
+      <c r="H9" s="14">
+        <v>200</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>255</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46238</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14">
+        <v>45</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>100</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>300</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>205</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46239</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>45</v>
+      </c>
+      <c r="D11" s="14">
+        <v>100</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>400</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1335</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>105</v>
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
@@ -1202,21 +1280,37 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46240</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>35</v>
+      </c>
+      <c r="D12" s="14">
+        <v>60</v>
+      </c>
+      <c r="E12" s="14">
+        <v>100</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>400</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1315</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>125</v>
       </c>
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
@@ -1224,21 +1318,37 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46241</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>65</v>
+      </c>
+      <c r="D13" s="14">
+        <v>250</v>
+      </c>
+      <c r="E13" s="14">
+        <v>120</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>500</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>85</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
@@ -1246,21 +1356,37 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46242</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>55</v>
+      </c>
+      <c r="D14" s="14">
+        <v>300</v>
+      </c>
+      <c r="E14" s="14">
+        <v>200</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>300</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1275</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>165</v>
       </c>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
@@ -1268,21 +1394,37 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>75</v>
+      </c>
+      <c r="D15" s="14">
+        <v>140</v>
+      </c>
+      <c r="E15" s="14">
+        <v>300</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>400</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1335</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>105</v>
       </c>
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
@@ -1290,21 +1432,37 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46244</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>85</v>
+      </c>
+      <c r="D16" s="14">
+        <v>200</v>
+      </c>
+      <c r="E16" s="14">
+        <v>200</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>300</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1405</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>35</v>
       </c>
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
@@ -1312,21 +1470,37 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>25</v>
+      </c>
+      <c r="D17" s="14">
+        <v>300</v>
+      </c>
+      <c r="E17" s="14">
+        <v>100</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>300</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1395</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>45</v>
       </c>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
@@ -1334,21 +1508,37 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>75</v>
+      </c>
+      <c r="D18" s="14">
+        <v>160</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>250</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>300</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>205</v>
       </c>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
@@ -1356,21 +1546,37 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>65</v>
+      </c>
+      <c r="D19" s="14">
+        <v>200</v>
+      </c>
+      <c r="E19" s="14">
+        <v>40</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>400</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1425</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>15</v>
       </c>
       <c r="K19" s="16"/>
       <c r="L19" s="16"/>
@@ -1378,21 +1584,37 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>95</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>500</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>255</v>
       </c>
       <c r="K20" s="16"/>
       <c r="L20" s="16"/>
@@ -1400,21 +1622,37 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>45</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>400</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>425</v>
       </c>
       <c r="K21" s="16"/>
       <c r="L21" s="16"/>
@@ -1422,21 +1660,37 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>75</v>
+      </c>
+      <c r="D22" s="14">
+        <v>140</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>600</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1265</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>175</v>
       </c>
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
@@ -1444,21 +1698,37 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>85</v>
+      </c>
+      <c r="D23" s="14">
+        <v>300</v>
+      </c>
+      <c r="E23" s="14">
+        <v>20</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>300</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1425</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>15</v>
       </c>
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
@@ -1466,21 +1736,37 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>75</v>
+      </c>
+      <c r="D24" s="14">
+        <v>200</v>
+      </c>
+      <c r="E24" s="14">
+        <v>100</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>300</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1345</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>95</v>
       </c>
       <c r="K24" s="16"/>
       <c r="L24" s="16"/>
@@ -1488,21 +1774,37 @@
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>85</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>150</v>
+      </c>
+      <c r="F25" s="14">
+        <v>200</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>400</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1375</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>65</v>
       </c>
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
@@ -1510,21 +1812,37 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>95</v>
+      </c>
+      <c r="D26" s="14">
+        <v>200</v>
+      </c>
+      <c r="E26" s="14">
+        <v>50</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>300</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1365</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>75</v>
       </c>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
@@ -1532,21 +1850,37 @@
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>75</v>
+      </c>
+      <c r="D27" s="14">
+        <v>140</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>400</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>345</v>
       </c>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
@@ -1554,21 +1888,37 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>45</v>
+      </c>
+      <c r="D28" s="14">
+        <v>200</v>
+      </c>
+      <c r="E28" s="14">
+        <v>120</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>500</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1285</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>155</v>
       </c>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
@@ -1576,21 +1926,37 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>45</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>150</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>500</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>205</v>
       </c>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
@@ -1598,21 +1964,37 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>45</v>
+      </c>
+      <c r="D30" s="14">
+        <v>140</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>300</v>
+      </c>
+      <c r="G30" s="14">
+        <v>6</v>
+      </c>
+      <c r="H30" s="14">
+        <v>400</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1335</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>105</v>
       </c>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
@@ -1620,21 +2002,37 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>45</v>
+      </c>
+      <c r="D31" s="14">
+        <v>160</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>500</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1405</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>35</v>
       </c>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
@@ -1642,21 +2040,37 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>45</v>
+      </c>
+      <c r="D32" s="14">
+        <v>180</v>
+      </c>
+      <c r="E32" s="14">
+        <v>40</v>
+      </c>
+      <c r="F32" s="14">
+        <v>200</v>
+      </c>
+      <c r="G32" s="14">
+        <v>4</v>
+      </c>
+      <c r="H32" s="14">
+        <v>400</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1285</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>155</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
@@ -1664,21 +2078,37 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>45</v>
+      </c>
+      <c r="D33" s="14">
+        <v>200</v>
+      </c>
+      <c r="E33" s="14">
+        <v>100</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>200</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1265</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>175</v>
       </c>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
@@ -1686,21 +2116,37 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>45</v>
+      </c>
+      <c r="D34" s="14">
+        <v>320</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>500</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1315</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>125</v>
       </c>
       <c r="K34" s="16"/>
       <c r="L34" s="16"/>
@@ -1708,21 +2154,37 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>75</v>
+      </c>
+      <c r="D35" s="14">
+        <v>300</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>500</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>85</v>
       </c>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
@@ -1730,21 +2192,37 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>85</v>
+      </c>
+      <c r="D36" s="14">
+        <v>140</v>
+      </c>
+      <c r="E36" s="14">
+        <v>100</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>400</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>295</v>
       </c>
       <c r="K36" s="16"/>
       <c r="L36" s="16"/>
@@ -1752,21 +2230,37 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>95</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>120</v>
+      </c>
+      <c r="F37" s="14">
+        <v>300</v>
+      </c>
+      <c r="G37" s="14">
+        <v>6</v>
+      </c>
+      <c r="H37" s="14">
+        <v>300</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>85</v>
       </c>
       <c r="K37" s="16"/>
       <c r="L37" s="16"/>
@@ -9810,6 +10304,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF1C6184-BFA1-4462-AA6E-BD26033A067E}"/>
+  <xr:revisionPtr revIDLastSave="383" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{191E38AC-4A36-4D41-8267-49B9D43EBC7B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>bad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">terrible </t>
   </si>
 </sst>
 </file>
@@ -1274,10 +1277,18 @@
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+      <c r="K11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
@@ -1312,10 +1323,16 @@
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
+      <c r="K12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+      <c r="N12" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
@@ -1350,10 +1367,16 @@
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
+      <c r="K13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
@@ -1388,10 +1411,16 @@
         <f t="shared" si="1"/>
         <v>165</v>
       </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
+      <c r="K14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+      <c r="N14" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
@@ -1426,10 +1455,16 @@
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
+      <c r="K15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+      <c r="N15" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
@@ -1464,10 +1499,16 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+      <c r="K16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+      <c r="N16" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
@@ -1502,10 +1543,16 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
+      <c r="K17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
@@ -1540,10 +1587,16 @@
         <f t="shared" si="1"/>
         <v>205</v>
       </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
+      <c r="K18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+      <c r="N18" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
@@ -1578,10 +1631,16 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
+      <c r="K19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+      <c r="N19" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
@@ -1616,10 +1675,16 @@
         <f t="shared" si="1"/>
         <v>255</v>
       </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
+      <c r="K20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+      <c r="N20" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
@@ -1654,10 +1719,16 @@
         <f t="shared" si="1"/>
         <v>425</v>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
+      <c r="K21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+      <c r="N21" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
@@ -1692,10 +1763,16 @@
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
+      <c r="K22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+      <c r="N22" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13">
@@ -1730,10 +1807,16 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
+      <c r="K23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+      <c r="N23" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
@@ -1768,10 +1851,16 @@
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
+      <c r="K24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+      <c r="N24" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
@@ -1806,10 +1895,16 @@
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
+      <c r="K25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+      <c r="N25" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
@@ -1844,10 +1939,16 @@
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
+      <c r="K26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="N26" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
@@ -1882,10 +1983,16 @@
         <f t="shared" si="1"/>
         <v>345</v>
       </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
+      <c r="K27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+      <c r="N27" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
@@ -1920,10 +2027,16 @@
         <f t="shared" si="1"/>
         <v>155</v>
       </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
+      <c r="K28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+      <c r="N28" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
@@ -1958,10 +2071,16 @@
         <f t="shared" si="1"/>
         <v>205</v>
       </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
+      <c r="K29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="N29" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
@@ -1996,10 +2115,16 @@
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
+      <c r="K30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+      <c r="N30" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
@@ -2034,10 +2159,16 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
+      <c r="K31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+      <c r="N31" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
@@ -2072,10 +2203,16 @@
         <f t="shared" si="1"/>
         <v>155</v>
       </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
+      <c r="K32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+      <c r="N32" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13">
@@ -2110,10 +2247,16 @@
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="K33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+      <c r="N33" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
@@ -2148,10 +2291,16 @@
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="K34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+      <c r="N34" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
@@ -2186,10 +2335,16 @@
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="K35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+      <c r="N35" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
@@ -2224,10 +2379,16 @@
         <f t="shared" si="1"/>
         <v>295</v>
       </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="K36" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+      <c r="N36" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13">
@@ -2262,13 +2423,21 @@
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="K37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+      <c r="N37" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13">
+        <v>46266</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -2287,7 +2456,9 @@
       <c r="K38" s="16"/>
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="N38" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>

--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="383" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{191E38AC-4A36-4D41-8267-49B9D43EBC7B}"/>
+  <xr:revisionPtr revIDLastSave="393" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B7B8A3A-65AF-489F-9329-F979D0F4B746}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t xml:space="preserve">terrible </t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1332,9 @@
       <c r="L12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="16"/>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17" t="s">
         <v>62</v>
       </c>
@@ -1373,7 +1378,9 @@
       <c r="L13" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M13" s="16"/>
+      <c r="M13" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N13" s="17" t="s">
         <v>62</v>
       </c>
@@ -1417,7 +1424,9 @@
       <c r="L14" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="16"/>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N14" s="17" t="s">
         <v>62</v>
       </c>
@@ -1461,7 +1470,9 @@
       <c r="L15" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M15" s="16"/>
+      <c r="M15" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N15" s="17" t="s">
         <v>62</v>
       </c>
@@ -1505,7 +1516,9 @@
       <c r="L16" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="16"/>
+      <c r="M16" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N16" s="17" t="s">
         <v>62</v>
       </c>
@@ -1549,7 +1562,9 @@
       <c r="L17" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M17" s="16"/>
+      <c r="M17" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N17" s="17" t="s">
         <v>62</v>
       </c>
@@ -1593,7 +1608,9 @@
       <c r="L18" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M18" s="16"/>
+      <c r="M18" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N18" s="17" t="s">
         <v>62</v>
       </c>
@@ -1637,7 +1654,9 @@
       <c r="L19" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M19" s="16"/>
+      <c r="M19" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N19" s="17" t="s">
         <v>62</v>
       </c>
@@ -1681,7 +1700,9 @@
       <c r="L20" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M20" s="16"/>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="17" t="s">
         <v>62</v>
       </c>
